--- a/tests/fixtures/comb.xlsx
+++ b/tests/fixtures/comb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28638617-3090-44EF-8885-603DF2511FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391238E7-C035-465A-9E30-ECC3655A72D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data1" sheetId="1" r:id="rId1"/>
@@ -115,11 +115,13 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -130,7 +132,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,6 +175,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14996795556505021"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -211,7 +219,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -225,6 +232,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,30 +555,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -579,7 +587,7 @@
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="3">
@@ -596,7 +604,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
@@ -605,7 +613,7 @@
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="3">
@@ -621,7 +629,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
@@ -630,7 +638,7 @@
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E4">
@@ -647,7 +655,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
@@ -656,7 +664,7 @@
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E5">
@@ -673,7 +681,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
@@ -682,7 +690,7 @@
       <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E6">
@@ -699,7 +707,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
@@ -708,7 +716,7 @@
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="3">
@@ -724,7 +732,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -733,7 +741,7 @@
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E8">
@@ -750,7 +758,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
@@ -759,7 +767,7 @@
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E9">
@@ -776,7 +784,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B10" t="s">
@@ -785,7 +793,7 @@
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E10">
@@ -802,7 +810,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B11" t="s">
@@ -811,7 +819,7 @@
       <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="3">
@@ -827,7 +835,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B12" t="s">
@@ -836,7 +844,7 @@
       <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="3">
@@ -853,7 +861,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B13" t="s">
@@ -862,7 +870,7 @@
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="3">
@@ -878,7 +886,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B14" t="s">
@@ -887,7 +895,7 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E14">
@@ -904,7 +912,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B15" t="s">
@@ -913,7 +921,7 @@
       <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E15">
@@ -930,7 +938,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B16" t="s">
@@ -939,7 +947,7 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E16">
@@ -956,7 +964,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B17" t="s">
@@ -965,7 +973,7 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="3">
@@ -981,7 +989,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B18" t="s">
@@ -990,7 +998,7 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E18">
@@ -1007,7 +1015,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B19" t="s">
@@ -1016,7 +1024,7 @@
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E19">
@@ -1033,7 +1041,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B20" t="s">
@@ -1042,7 +1050,7 @@
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E20">
@@ -1059,7 +1067,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B21" t="s">
@@ -1068,7 +1076,7 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="3">
@@ -1084,33 +1092,33 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="9" t="s">
+      <c r="A22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="9">
+      <c r="D22" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="8">
         <f>ROUND(E21 * 1.25, 0)</f>
         <v>156</v>
       </c>
-      <c r="F22" s="9" t="e">
+      <c r="F22" s="8" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="G22" s="9" t="e">
+      <c r="G22" s="8" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B23" t="s">
@@ -1119,7 +1127,7 @@
       <c r="C23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E23">
@@ -1136,7 +1144,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B24" t="s">
@@ -1145,7 +1153,7 @@
       <c r="C24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E24">
@@ -1162,7 +1170,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B25" t="s">
@@ -1171,7 +1179,7 @@
       <c r="C25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E25">
@@ -1188,7 +1196,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B26" t="s">
@@ -1197,7 +1205,7 @@
       <c r="C26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E26">
@@ -1214,7 +1222,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B27" t="s">
@@ -1223,7 +1231,7 @@
       <c r="C27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E27">
@@ -1240,7 +1248,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B28" t="s">
@@ -1249,7 +1257,7 @@
       <c r="C28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E28">
@@ -1266,7 +1274,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B29" t="s">
@@ -1275,7 +1283,7 @@
       <c r="C29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E29">
@@ -1292,7 +1300,7 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B30" t="s">
@@ -1301,7 +1309,7 @@
       <c r="C30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E30">
@@ -1318,7 +1326,7 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B31" t="s">
@@ -1327,7 +1335,7 @@
       <c r="C31" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E31">
@@ -1344,7 +1352,7 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B32" t="s">
@@ -1353,7 +1361,7 @@
       <c r="C32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E32">
@@ -1370,7 +1378,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B33" t="s">
@@ -1379,7 +1387,7 @@
       <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E33">
@@ -1396,7 +1404,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B34" t="s">
@@ -1405,7 +1413,7 @@
       <c r="C34" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E34">
